--- a/data/satisfaction_detail/2026/1-8月/专业观众.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/专业观众.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.66</v>
+        <v>9.688782428776063</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.890000000000001</v>
+        <v>9.907980264204998</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.99</v>
+        <v>9.995097883176827</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.99</v>
+        <v>9.992121597962758</v>
       </c>
     </row>
     <row r="4">
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.99</v>
+        <v>9.993872353971033</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>9.98</v>
+        <v>9.98739455674041</v>
       </c>
     </row>
     <row r="5">
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.99</v>
+        <v>9.99264682476524</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9.99</v>
+        <v>9.99264682476524</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>9.99</v>
+        <v>9.991421295559446</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.99</v>
+        <v>9.993872353971033</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>9.4</v>
+        <v>9.403614515358905</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>9.82</v>
+        <v>9.837623216085735</v>
       </c>
     </row>
     <row r="9">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.226969069977187</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.68</v>
+        <v>9.712374131253648</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.19</v>
+        <v>9.023597007798823</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.77</v>
+        <v>9.800705607724547</v>
       </c>
     </row>
     <row r="11">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>9.550000000000001</v>
+        <v>9.586512812350787</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.889433922223992</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.289999999999999</v>
+        <v>9.297545227863548</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.81</v>
+        <v>9.832405963181071</v>
       </c>
     </row>
     <row r="13">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.449999999999999</v>
+        <v>9.477072523741313</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.83</v>
+        <v>9.844427821104567</v>
       </c>
     </row>
     <row r="14">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.25</v>
+        <v>9.314870815427875</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.789999999999999</v>
+        <v>9.809284312165101</v>
       </c>
     </row>
     <row r="15">
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9.9</v>
+        <v>9.894054326489469</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.971328452437795</v>
       </c>
     </row>
     <row r="16">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9.6</v>
+        <v>9.671180433975277</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9.859999999999999</v>
+        <v>9.899588307071992</v>
       </c>
     </row>
     <row r="17">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>8.98</v>
+        <v>9.09020107167489</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.84</v>
+        <v>9.84558332007003</v>
       </c>
     </row>
     <row r="18">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>9.449999999999999</v>
+        <v>9.452649869678542</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>9.6</v>
+        <v>9.697624190064795</v>
       </c>
     </row>
     <row r="19">
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>9.99</v>
+        <v>9.995097883176827</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>9.99</v>
+        <v>9.995097883176827</v>
       </c>
     </row>
     <row r="20">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>9.99</v>
+        <v>9.996323412382621</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>9.99</v>
+        <v>9.996323412382621</v>
       </c>
     </row>
     <row r="21">
